--- a/archivos_vqd/Listado de VQDs Soporte Apodaca.xlsx
+++ b/archivos_vqd/Listado de VQDs Soporte Apodaca.xlsx
@@ -582,97 +582,97 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
       <c r="D16" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
       <c r="D17" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75" customFormat="1" s="1">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5" customFormat="1" s="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="3"/>
       <c r="D25" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="3"/>
       <c r="D26" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
       <c r="C27" s="3"/>
       <c r="D27" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
       <c r="D28" s="4"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="3"/>
